--- a/data/trans_dic/P36B08_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,57; 66,65</t>
+          <t>55,23; 67,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65,76; 76,17</t>
+          <t>65,34; 76,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,34; 85,29</t>
+          <t>74,48; 85,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,9; 96,3</t>
+          <t>90,44; 96,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,06; 76,8</t>
+          <t>65,47; 76,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,34; 83,62</t>
+          <t>73,53; 84,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,81; 89,71</t>
+          <t>80,99; 89,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>89,43; 97,89</t>
+          <t>93,17; 98,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61,96; 70,44</t>
+          <t>61,78; 69,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71,29; 78,47</t>
+          <t>71,02; 78,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79,34; 86,09</t>
+          <t>79,39; 86,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,78; 96,52</t>
+          <t>93,0; 96,89</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,02; 49,93</t>
+          <t>40,72; 50,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,83; 60,69</t>
+          <t>51,4; 60,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,83; 72,25</t>
+          <t>64,15; 72,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,02; 95,14</t>
+          <t>90,2; 95,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,89; 61,99</t>
+          <t>53,63; 62,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,82; 71,4</t>
+          <t>63,28; 71,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,98; 82,32</t>
+          <t>74,97; 82,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,94; 94,95</t>
+          <t>91,29; 95,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48,73; 54,83</t>
+          <t>48,54; 55,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58,63; 64,86</t>
+          <t>58,54; 64,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,86; 76,2</t>
+          <t>71,02; 76,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>90,82; 94,56</t>
+          <t>91,51; 94,77</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67,84; 77,89</t>
+          <t>67,38; 77,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,83; 84,32</t>
+          <t>75,12; 83,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,78; 77,82</t>
+          <t>68,14; 77,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,65; 94,19</t>
+          <t>88,26; 94,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,12; 81,41</t>
+          <t>71,87; 81,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,67; 89,42</t>
+          <t>81,75; 89,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,18; 81,87</t>
+          <t>73,69; 82,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>92,16; 96,35</t>
+          <t>92,25; 96,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71,66; 78,19</t>
+          <t>71,45; 78,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79,78; 85,76</t>
+          <t>79,93; 85,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71,87; 78,8</t>
+          <t>72,04; 78,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90,84; 94,62</t>
+          <t>91,36; 94,82</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,48; 72,97</t>
+          <t>62,99; 72,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73,46; 82,66</t>
+          <t>73,0; 82,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,88; 84,24</t>
+          <t>75,82; 84,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95,68; 99,38</t>
+          <t>96,58; 99,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,48; 81,61</t>
+          <t>73,5; 81,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,53; 88,61</t>
+          <t>81,61; 88,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,25; 90,23</t>
+          <t>83,11; 90,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96,83; 99,31</t>
+          <t>96,11; 98,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,1; 76,26</t>
+          <t>69,74; 76,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78,88; 84,64</t>
+          <t>79,11; 84,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>80,9; 86,27</t>
+          <t>80,86; 86,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,08; 99,18</t>
+          <t>96,77; 98,98</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,85; 57,99</t>
+          <t>43,2; 57,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,85; 70,54</t>
+          <t>56,93; 70,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85,08; 93,55</t>
+          <t>84,16; 93,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98,36; 100,0</t>
+          <t>98,55; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,76; 69,26</t>
+          <t>54,96; 69,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,62; 78,93</t>
+          <t>66,56; 78,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,82; 93,24</t>
+          <t>84,96; 93,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>97,78; 99,8</t>
+          <t>97,91; 99,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,77; 61,75</t>
+          <t>51,85; 61,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,51; 73,45</t>
+          <t>63,05; 72,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86,76; 92,47</t>
+          <t>86,69; 92,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,61; 99,82</t>
+          <t>98,63; 99,88</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,85; 70,17</t>
+          <t>58,41; 70,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67,11; 77,46</t>
+          <t>66,24; 78,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,24; 60,25</t>
+          <t>48,28; 60,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94,06; 98,42</t>
+          <t>94,03; 98,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70,71; 80,98</t>
+          <t>71,03; 81,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,28; 87,28</t>
+          <t>78,36; 87,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,98; 65,82</t>
+          <t>54,17; 66,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95,23; 99,11</t>
+          <t>95,61; 99,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,91; 74,18</t>
+          <t>66,33; 74,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74,21; 81,37</t>
+          <t>74,0; 81,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52,53; 61,29</t>
+          <t>52,71; 61,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95,66; 98,39</t>
+          <t>95,94; 98,44</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,02; 79,21</t>
+          <t>72,11; 78,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,56; 77,46</t>
+          <t>70,13; 77,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59,32; 67,46</t>
+          <t>59,53; 67,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83,96; 90,47</t>
+          <t>85,04; 90,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,16; 78,19</t>
+          <t>71,44; 78,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,87; 85,09</t>
+          <t>79,01; 85,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,65; 75,06</t>
+          <t>68,15; 75,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90,56; 97,16</t>
+          <t>89,7; 93,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,54; 77,75</t>
+          <t>72,81; 77,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75,89; 80,58</t>
+          <t>75,79; 80,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65,29; 70,41</t>
+          <t>65,06; 70,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,77; 94,68</t>
+          <t>88,0; 91,67</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>57,79; 65,37</t>
+          <t>58,36; 65,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69,24; 76,07</t>
+          <t>69,1; 75,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,85; 79,23</t>
+          <t>73,33; 79,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96,7; 99,39</t>
+          <t>95,98; 98,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>68,06; 74,41</t>
+          <t>67,71; 74,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>76,99; 82,96</t>
+          <t>77,2; 83,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,06; 79,21</t>
+          <t>72,87; 79,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>96,86; 98,78</t>
+          <t>96,91; 98,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>63,94; 69,04</t>
+          <t>64,19; 69,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74,29; 78,48</t>
+          <t>74,33; 78,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74,06; 78,37</t>
+          <t>73,8; 78,35</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>97,28; 98,96</t>
+          <t>96,95; 98,56</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61,48; 64,97</t>
+          <t>61,68; 64,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69,51; 72,71</t>
+          <t>69,56; 72,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>70,75; 73,79</t>
+          <t>70,84; 73,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93,31; 95,72</t>
+          <t>93,49; 95,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>69,3; 72,52</t>
+          <t>69,41; 72,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>78,13; 80,83</t>
+          <t>78,08; 80,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>76,06; 78,81</t>
+          <t>75,86; 78,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>95,18; 96,74</t>
+          <t>95,08; 96,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66,1; 68,46</t>
+          <t>65,9; 68,27</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74,36; 76,5</t>
+          <t>74,4; 76,46</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73,82; 75,98</t>
+          <t>73,76; 75,88</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>94,43; 95,93</t>
+          <t>94,46; 95,57</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291388</t>
+          <t>299982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>276740</t>
+          <t>304929</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>568127</t>
+          <t>604911</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>148531; 181414</t>
+          <t>150335; 182830</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>193818; 224488</t>
+          <t>192592; 224227</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>220603; 249757</t>
+          <t>218086; 249896</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>273773; 299916</t>
+          <t>288372; 306954</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>169701; 200317</t>
+          <t>170774; 199580</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>209178; 238475</t>
+          <t>209709; 239632</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>231700; 257221</t>
+          <t>232215; 256634</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>259017; 283524</t>
+          <t>294478; 309909</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>330254; 375450</t>
+          <t>329315; 372772</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>413419; 455081</t>
+          <t>411902; 454830</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>459789; 498906</t>
+          <t>460070; 498690</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>545685; 580142</t>
+          <t>590479; 615191</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481243</t>
+          <t>494236</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>479967</t>
+          <t>511201</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>961209</t>
+          <t>1005438</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>202274; 246203</t>
+          <t>200774; 247549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>262027; 306782</t>
+          <t>259818; 306529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>317614; 359518</t>
+          <t>319244; 361344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>461493; 493210</t>
+          <t>478640; 507564</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>266518; 312387</t>
+          <t>270262; 313017</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>329004; 373970</t>
+          <t>331414; 374159</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>390361; 428594</t>
+          <t>390316; 428427</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>468316; 488984</t>
+          <t>498887; 519616</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>485834; 546645</t>
+          <t>483992; 548796</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>603440; 667555</t>
+          <t>602568; 667788</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>721549; 775944</t>
+          <t>723206; 779016</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>938487; 977164</t>
+          <t>985660; 1020762</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288586</t>
+          <t>290285</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>328045</t>
+          <t>335656</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>616631</t>
+          <t>625941</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>216291; 248343</t>
+          <t>214830; 245637</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>244935; 272376</t>
+          <t>242659; 270386</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215312; 247201</t>
+          <t>216431; 245946</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>277033; 297675</t>
+          <t>278906; 298711</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>241889; 273067</t>
+          <t>241049; 272968</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>278513; 304928</t>
+          <t>278797; 305644</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>246111; 275347</t>
+          <t>247832; 278481</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>319879; 334411</t>
+          <t>326875; 341813</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>468847; 511534</t>
+          <t>467470; 511968</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>529781; 569480</t>
+          <t>530788; 569180</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>469985; 515340</t>
+          <t>471139; 513134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>602415; 627484</t>
+          <t>612377; 635565</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306122</t>
+          <t>366680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>468218</t>
+          <t>413471</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>774340</t>
+          <t>780152</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>227669; 261735</t>
+          <t>225925; 261687</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274727; 309142</t>
+          <t>273009; 308038</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>280735; 311661</t>
+          <t>280510; 311525</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>298329; 309882</t>
+          <t>359638; 370343</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>272951; 303135</t>
+          <t>273019; 303257</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>317101; 344660</t>
+          <t>317424; 346140</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>321602; 348589</t>
+          <t>321067; 348408</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>460629; 472421</t>
+          <t>405568; 417590</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511831; 556774</t>
+          <t>509158; 556998</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>601823; 645735</t>
+          <t>603530; 647133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>611873; 652437</t>
+          <t>611549; 651807</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>764559; 781085</t>
+          <t>768682; 786239</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178227</t>
+          <t>205150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>206420</t>
+          <t>224854</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>384647</t>
+          <t>430005</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>89155; 117889</t>
+          <t>87835; 116987</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>120873; 149985</t>
+          <t>121052; 149803</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>179716; 197595</t>
+          <t>177758; 197441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>175811; 178742</t>
+          <t>202686; 205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>115803; 143825</t>
+          <t>114130; 144506</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>146294; 173315</t>
+          <t>146150; 172171</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>185398; 203818</t>
+          <t>185721; 203992</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>203341; 207552</t>
+          <t>221747; 226057</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212776; 253766</t>
+          <t>213085; 252342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>278821; 317476</t>
+          <t>272490; 314342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>372898; 397439</t>
+          <t>372612; 397688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>381320; 386031</t>
+          <t>426222; 431645</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261124</t>
+          <t>262060</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>251492</t>
+          <t>258330</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>512616</t>
+          <t>520390</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>159385; 190022</t>
+          <t>158177; 189556</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>183879; 212239</t>
+          <t>181493; 213771</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>126455; 157920</t>
+          <t>126544; 157836</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253627; 265368</t>
+          <t>254538; 266102</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>196687; 225250</t>
+          <t>197577; 226245</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>217683; 242720</t>
+          <t>217904; 243718</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>146839; 179057</t>
+          <t>147359; 181528</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>244783; 254781</t>
+          <t>252169; 261412</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>361842; 407190</t>
+          <t>364130; 406773</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>409724; 449213</t>
+          <t>408522; 447336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>280561; 327370</t>
+          <t>281544; 329259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>503836; 518224</t>
+          <t>512737; 526103</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>545559</t>
+          <t>631741</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>795402</t>
+          <t>709933</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1340961</t>
+          <t>1341674</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>442942; 487182</t>
+          <t>443475; 485422</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>464055; 509374</t>
+          <t>461221; 510016</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>386406; 439405</t>
+          <t>387763; 439460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>522456; 562964</t>
+          <t>609316; 651523</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>454168; 499048</t>
+          <t>455915; 498827</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>543546; 586397</t>
+          <t>544522; 587590</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>469511; 513321</t>
+          <t>466056; 515798</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>769098; 825109</t>
+          <t>692499; 723776</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>909157; 974382</t>
+          <t>912491; 972457</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1022140; 1085308</t>
+          <t>1020770; 1084536</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>871849; 940154</t>
+          <t>868770; 940951</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1306247; 1393192</t>
+          <t>1309912; 1364521</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>911649</t>
+          <t>779115</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>701933</t>
+          <t>813584</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1613582</t>
+          <t>1592699</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>429874; 486232</t>
+          <t>434095; 486339</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>538767; 591875</t>
+          <t>537618; 589049</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>564153; 613606</t>
+          <t>567912; 614010</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>897380; 922322</t>
+          <t>765304; 786736</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>532505; 582206</t>
+          <t>529833; 583163</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>633393; 682550</t>
+          <t>635086; 683072</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>601545; 652116</t>
+          <t>599907; 650769</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>693678; 707404</t>
+          <t>803996; 820134</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>975880; 1053693</t>
+          <t>979636; 1054132</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1189150; 1256291</t>
+          <t>1189789; 1258205</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1183296; 1252102</t>
+          <t>1179155; 1251867</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1599469; 1627113</t>
+          <t>1577313; 1603488</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3263898</t>
+          <t>3329251</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3508214</t>
+          <t>3571959</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6772113</t>
+          <t>6901209</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2013745; 2128375</t>
+          <t>2020508; 2125928</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2376920; 2486475</t>
+          <t>2378762; 2487264</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2389348; 2491913</t>
+          <t>2392468; 2498647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3225292; 3308458</t>
+          <t>3298351; 3361511</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2341215; 2449848</t>
+          <t>2344836; 2451375</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2772253; 2868338</t>
+          <t>2770591; 2869215</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2683182; 2780348</t>
+          <t>2676208; 2778115</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3481519; 3538720</t>
+          <t>3547249; 3595058</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4397999; 4555090</t>
+          <t>4385114; 4542259</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5181387; 5330806</t>
+          <t>5183933; 5328090</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5097210; 5246277</t>
+          <t>5092834; 5239708</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6717872; 6824431</t>
+          <t>6856932; 6937159</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B08_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
